--- a/veterinarian_forms/025_veterinary_client_satisfaction_benchmark_survey--veterinarian_forms.xlsx
+++ b/veterinarian_forms/025_veterinary_client_satisfaction_benchmark_survey--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your name</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Was the staff helpful?</t>
+          <t>Do you have any additional comments or suggestions for our clinic?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Was the staff knowledgeable?</t>
+          <t>What could we have done to improve your visit?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Was the waiting time reasonable?</t>
+          <t>How can we improve our clinic?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How satisfied are you with the quality of care provided by our clinic?</t>
+          <t>Was the waiting time reasonable?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How likely are you to return to our clinic for future visits?</t>
+          <t>How satisfied are you with the quality of care provided by our clinic?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How likely are you to recommend a friend or family member to our clinic?</t>
+          <t>How likely are you to return to our clinic for future visits?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Do you have any additional comments or suggestions for our clinic?</t>
+          <t>Was the staff helpful and knowledgeable?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Is there anything we could have done to improve your visit?</t>
+          <t>Additional comments or suggestions?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How can we improve our clinic?</t>
+          <t>Question 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,126 +962,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What time did you arrive at the clinic?</t>
+          <t>Question 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What time did you leave the clinic?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How long did your visit take?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Was the staff friendly?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Was the staff helpful?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Was the staff knowledgeable?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_not_at_all'}</t>
+          <t>1_-_not_at_all</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - Not at all'}</t>
+          <t>1 - Not at all</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_slightly'}</t>
+          <t>2_-_slightly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Slightly'}</t>
+          <t>2 - Slightly</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat'}</t>
+          <t>4_-_somewhat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat'}</t>
+          <t>4 - Somewhat</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_highly'}</t>
+          <t>5_-_highly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '5 - Highly'}</t>
+          <t>5 - Highly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_very_dissatisfied'}</t>
+          <t>1_-_very_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1 - Very dissatisfied'}</t>
+          <t>1 - Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_somewhat_dissatisfied'}</t>
+          <t>2_-_somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2 - Somewhat dissatisfied'}</t>
+          <t>2 - Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_somewhat_satisfied'}</t>
+          <t>4_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '4 - Somewhat satisfied'}</t>
+          <t>4 - Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_very_satisfied'}</t>
+          <t>5_-_very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '5 - Very satisfied'}</t>
+          <t>5 - Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'initial_exam'}</t>
+          <t>initial_exam</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Initial Exam'}</t>
+          <t>Initial Exam</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'vaccination'}</t>
+          <t>vaccination</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Vaccination'}</t>
+          <t>Vaccination</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'routine_check-up'}</t>
+          <t>routine_check-up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Routine Check-up'}</t>
+          <t>Routine Check-up</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medical_procedure'}</t>
+          <t>medical_procedure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medical Procedure'}</t>
+          <t>Medical Procedure</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_describe)'}</t>
+          <t>other_(please_describe)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please describe)'}</t>
+          <t>Other (please describe)</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1403,488 +1288,267 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>less_than_15_minutes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Less than 15 minutes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>between_15-30_minutes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Between 15-30 minutes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>more_than_30_minutes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>More than 30 minutes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_15_minutes'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 15 minutes'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'between_15-30_minutes'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Between 15-30 minutes'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_30_minutes'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'More than 30 minutes'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>highly_likely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Highly likely</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'likely'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'very_likely'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'Very likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'highly_likely'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'Highly likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'not_at_all'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'Not at all'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'somewhat'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'Somewhat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'likely'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'very_likely'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'Very Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'highly'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'Highly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
